--- a/analysis/tables/bloom-1b7.xlsx
+++ b/analysis/tables/bloom-1b7.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8529826036989322</v>
+        <v>0.6880726336504724</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2099476468170498</v>
+        <v>-0.1701417919777667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.853x - 0.210</t>
+          <t>y = 0.688x - 0.170</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7400733070297351</v>
+        <v>0.7400733070297357</v>
       </c>
       <c r="H3" t="n">
         <v>0.08083484371271089</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2461335622867553</v>
+        <v>0.2472730110992838</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6430349568818824</v>
+        <v>0.5179308416727058</v>
       </c>
       <c r="K3" t="n">
         <v>0.1302671269017737</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8257978031026181</v>
+        <v>0.6822021167507898</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.077237895314617</v>
+        <v>-0.1609828528661669</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.826x - 0.077</t>
+          <t>y = 0.682x - 0.161</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7723375754511835</v>
+        <v>0.7434380683738435</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07969976409868626</v>
+        <v>0.08071646904641239</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09353124339205708</v>
+        <v>0.2359753054313292</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7485599077880011</v>
+        <v>0.5212192638846229</v>
       </c>
       <c r="K4" t="n">
         <v>0.1302671269017737</v>
